--- a/Deliverables/Stadium_Board/BOM/Client_BOM.xlsx
+++ b/Deliverables/Stadium_Board/BOM/Client_BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="155">
   <si>
     <t>Bill of Material (BOM) for Stadium_Board</t>
   </si>
@@ -414,12 +414,6 @@
     <t>TDK</t>
   </si>
   <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
     <t xml:space="preserve">Samsung </t>
   </si>
   <si>
@@ -484,6 +478,12 @@
   </si>
   <si>
     <t>--------</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R8BB475</t>
+  </si>
+  <si>
+    <t>ESR25JZPF5600</t>
   </si>
 </sst>
 </file>
@@ -585,7 +585,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,6 +601,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1023,7 +1029,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1237,24 +1243,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1267,9 +1255,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1306,42 +1291,6 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1351,9 +1300,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1361,6 +1307,99 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1649,7 +1688,7 @@
     <col min="5" max="5" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="21.7109375" bestFit="1" customWidth="1"/>
@@ -1663,26 +1702,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="102"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="101"/>
     </row>
     <row r="2" spans="1:18" ht="16.5" thickBot="1">
       <c r="A2" s="2" t="s">
@@ -1744,13 +1783,13 @@
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="80" t="s">
+      <c r="C3" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="105" t="s">
         <v>49</v>
       </c>
       <c r="E3" s="22" t="s">
@@ -1800,11 +1839,11 @@
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="78" t="s">
+      <c r="B4" s="103"/>
+      <c r="C4" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="106" t="s">
         <v>53</v>
       </c>
       <c r="E4" s="9" t="s">
@@ -1854,11 +1893,11 @@
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="104"/>
-      <c r="C5" s="78" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="106" t="s">
         <v>57</v>
       </c>
       <c r="E5" s="9" t="s">
@@ -1909,24 +1948,24 @@
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="104"/>
-      <c r="C6" s="78" t="s">
+      <c r="B6" s="103"/>
+      <c r="C6" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="106" t="s">
         <v>60</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="122" t="s">
         <v>62</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>130</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>94</v>
@@ -1938,25 +1977,25 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>131</v>
+      <c r="L6" s="7">
+        <v>10</v>
+      </c>
+      <c r="M6" s="121" t="s">
+        <v>126</v>
       </c>
       <c r="N6" s="17">
-        <v>0.36</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="O6" s="17">
-        <f>N6*J6</f>
-        <v>0.72</v>
+        <f>N6*L6</f>
+        <v>0.57000000000000006</v>
       </c>
       <c r="P6" s="17">
-        <v>0.25</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="Q6" s="17">
         <f>P6*K6</f>
-        <v>10</v>
+        <v>2.2800000000000002</v>
       </c>
       <c r="R6" s="29"/>
     </row>
@@ -1964,26 +2003,26 @@
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="104"/>
-      <c r="C7" s="111" t="s">
+      <c r="B7" s="103"/>
+      <c r="C7" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="112" t="s">
+      <c r="D7" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="112" t="s">
+      <c r="E7" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="112" t="s">
+      <c r="F7" s="92" t="s">
         <v>66</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="112" t="s">
+      <c r="I7" s="92" t="s">
         <v>95</v>
       </c>
       <c r="J7" s="16">
@@ -2018,11 +2057,11 @@
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="82" t="s">
+      <c r="B8" s="104"/>
+      <c r="C8" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="108" t="s">
         <v>68</v>
       </c>
       <c r="E8" s="30" t="s">
@@ -2032,7 +2071,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H8" s="31" t="s">
         <v>127</v>
@@ -2051,7 +2090,7 @@
         <v>50</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N8" s="35">
         <v>0.08</v>
@@ -2073,13 +2112,13 @@
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="80" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="83" t="s">
+      <c r="C9" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="109" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="37" t="s">
@@ -2089,7 +2128,7 @@
         <v>71</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H9" s="38" t="s">
         <v>127</v>
@@ -2123,19 +2162,19 @@
         <f>P9*L9</f>
         <v>4.1050000000000004</v>
       </c>
-      <c r="R9" s="90"/>
+      <c r="R9" s="83"/>
     </row>
     <row r="10" spans="1:18" ht="16.5" thickBot="1">
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="110" t="s">
         <v>27</v>
       </c>
       <c r="E10" s="42" t="s">
@@ -2145,7 +2184,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H10" s="43" t="s">
         <v>127</v>
@@ -2185,13 +2224,13 @@
       <c r="A11" s="2">
         <v>9</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="83" t="s">
+      <c r="C11" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="109" t="s">
         <v>73</v>
       </c>
       <c r="E11" s="37" t="s">
@@ -2235,19 +2274,19 @@
         <f>P11*L11</f>
         <v>7.516</v>
       </c>
-      <c r="R11" s="90"/>
+      <c r="R11" s="83"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" thickBot="1">
       <c r="A12" s="2">
         <v>10</v>
       </c>
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="82" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="85" t="s">
+      <c r="C12" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="111" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="56" t="s">
@@ -2257,10 +2296,10 @@
         <v>25</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H12" s="57" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I12" s="56" t="s">
         <v>118</v>
@@ -2276,7 +2315,7 @@
         <v>55</v>
       </c>
       <c r="M12" s="60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N12" s="61">
         <v>3.4289999999999998</v>
@@ -2296,13 +2335,13 @@
       <c r="A13" s="2">
         <v>11</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="93" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="105" t="s">
         <v>76</v>
       </c>
       <c r="E13" s="22" t="s">
@@ -2312,7 +2351,7 @@
         <v>78</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>127</v>
@@ -2353,11 +2392,11 @@
       <c r="A14" s="2">
         <v>12</v>
       </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="78" t="s">
+      <c r="B14" s="94"/>
+      <c r="C14" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="106" t="s">
         <v>80</v>
       </c>
       <c r="E14" s="9" t="s">
@@ -2367,7 +2406,7 @@
         <v>81</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>127</v>
@@ -2408,11 +2447,11 @@
       <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="95"/>
-      <c r="C15" s="78" t="s">
+      <c r="B15" s="94"/>
+      <c r="C15" s="72" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="106" t="s">
         <v>83</v>
       </c>
       <c r="E15" s="9" t="s">
@@ -2422,7 +2461,7 @@
         <v>84</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>127</v>
@@ -2463,11 +2502,11 @@
       <c r="A16" s="2">
         <v>14</v>
       </c>
-      <c r="B16" s="95"/>
-      <c r="C16" s="78" t="s">
+      <c r="B16" s="94"/>
+      <c r="C16" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="106" t="s">
         <v>86</v>
       </c>
       <c r="E16" s="9" t="s">
@@ -2477,7 +2516,7 @@
         <v>88</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>127</v>
@@ -2492,25 +2531,25 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="L16" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>131</v>
+      <c r="L16" s="7">
+        <v>100</v>
+      </c>
+      <c r="M16" s="121" t="s">
+        <v>126</v>
       </c>
       <c r="N16" s="17">
-        <v>0.1</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="O16" s="17">
-        <f>N16*J16</f>
-        <v>0.2</v>
+        <f>N16*L16</f>
+        <v>0.09</v>
       </c>
       <c r="P16" s="17">
-        <v>1.4999999999999999E-2</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q16" s="17">
-        <f>P16*K16</f>
-        <v>0.6</v>
+        <f>P16*L16</f>
+        <v>0.09</v>
       </c>
       <c r="R16" s="51"/>
     </row>
@@ -2518,24 +2557,24 @@
       <c r="A17" s="2">
         <v>15</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="78" t="s">
+      <c r="B17" s="94"/>
+      <c r="C17" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="106" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="122" t="s">
         <v>31</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>32</v>
@@ -2548,23 +2587,24 @@
         <v>40</v>
       </c>
       <c r="L17" s="8">
-        <v>50</v>
-      </c>
-      <c r="M17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="121" t="s">
         <v>126</v>
       </c>
       <c r="N17" s="17">
-        <v>1.1900000000000001E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="O17" s="17">
-        <v>0.6</v>
+        <f>N17*L17</f>
+        <v>0.34599999999999997</v>
       </c>
       <c r="P17" s="17">
-        <v>1.1900000000000001E-2</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="Q17" s="17">
-        <f>P17*L17</f>
-        <v>0.59500000000000008</v>
+        <f>P17*K17</f>
+        <v>1.3839999999999999</v>
       </c>
       <c r="R17" s="51"/>
     </row>
@@ -2572,11 +2612,11 @@
       <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="96"/>
-      <c r="C18" s="86" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="30" t="s">
+      <c r="B18" s="95"/>
+      <c r="C18" s="79" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="108" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="30" t="s">
@@ -2586,7 +2626,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H18" s="31" t="s">
         <v>127</v>
@@ -2627,13 +2667,13 @@
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="112" t="s">
         <v>37</v>
       </c>
       <c r="E19" s="49" t="s">
@@ -2643,7 +2683,7 @@
         <v>104</v>
       </c>
       <c r="G19" s="50" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H19" s="20" t="s">
         <v>127</v>
@@ -2659,35 +2699,36 @@
         <v>40</v>
       </c>
       <c r="L19" s="21">
-        <v>40</v>
-      </c>
-      <c r="M19" s="109" t="s">
-        <v>126</v>
-      </c>
-      <c r="N19" s="110">
-        <v>0.53739999999999999</v>
-      </c>
-      <c r="O19" s="110">
-        <v>0.54</v>
-      </c>
-      <c r="P19" s="110">
-        <v>0.36609999999999998</v>
-      </c>
-      <c r="Q19" s="110">
-        <f>P19*L19</f>
-        <v>14.643999999999998</v>
-      </c>
-      <c r="R19" s="91"/>
+        <v>20</v>
+      </c>
+      <c r="M19" s="123" t="s">
+        <v>148</v>
+      </c>
+      <c r="N19" s="90">
+        <v>0.70850000000000002</v>
+      </c>
+      <c r="O19" s="90">
+        <f>N19*L19</f>
+        <v>14.17</v>
+      </c>
+      <c r="P19" s="90">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="Q19" s="90">
+        <f>P19*K19</f>
+        <v>21.36</v>
+      </c>
+      <c r="R19" s="84"/>
     </row>
     <row r="20" spans="1:19" ht="16.5" thickBot="1">
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="78" t="s">
+      <c r="B20" s="94"/>
+      <c r="C20" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="106" t="s">
         <v>106</v>
       </c>
       <c r="E20" s="9" t="s">
@@ -2697,7 +2738,7 @@
         <v>108</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>127</v>
@@ -2737,11 +2778,11 @@
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="78" t="s">
+      <c r="B21" s="94"/>
+      <c r="C21" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="106" t="s">
         <v>110</v>
       </c>
       <c r="E21" s="9" t="s">
@@ -2751,7 +2792,7 @@
         <v>38</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>127</v>
@@ -2791,18 +2832,18 @@
       <c r="A22" s="2">
         <v>20</v>
       </c>
-      <c r="B22" s="96"/>
-      <c r="C22" s="79" t="s">
+      <c r="B22" s="95"/>
+      <c r="C22" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="D22" s="63" t="s">
+      <c r="D22" s="113" t="s">
         <v>112</v>
       </c>
       <c r="E22" s="63" t="s">
         <v>113</v>
       </c>
       <c r="F22" s="63" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>127</v>
@@ -2824,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="M22" s="67" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N22" s="68">
         <v>9.59</v>
@@ -2839,29 +2880,29 @@
         <f t="shared" si="1"/>
         <v>160.45000000000002</v>
       </c>
-      <c r="R22" s="92"/>
+      <c r="R22" s="85"/>
     </row>
     <row r="23" spans="1:19" s="13" customFormat="1" ht="16.5" thickBot="1">
       <c r="A23" s="2">
         <v>21</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="106" t="s">
+      <c r="C23" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="107" t="s">
+      <c r="D23" s="114" t="s">
         <v>40</v>
       </c>
-      <c r="E23" s="107" t="s">
+      <c r="E23" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="107" t="s">
+      <c r="F23" s="88" t="s">
         <v>41</v>
       </c>
       <c r="G23" s="69" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H23" s="23" t="s">
         <v>127</v>
@@ -2895,17 +2936,17 @@
         <f>P23*L23</f>
         <v>1.9040000000000001</v>
       </c>
-      <c r="R23" s="108"/>
+      <c r="R23" s="89"/>
     </row>
     <row r="24" spans="1:19" ht="16.5" thickBot="1">
       <c r="A24" s="2">
         <v>22</v>
       </c>
-      <c r="B24" s="95"/>
-      <c r="C24" s="78" t="s">
+      <c r="B24" s="94"/>
+      <c r="C24" s="72" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="106" t="s">
         <v>42</v>
       </c>
       <c r="E24" s="9" t="s">
@@ -2915,7 +2956,7 @@
         <v>43</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>127</v>
@@ -2934,7 +2975,7 @@
         <v>20</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N24" s="15">
         <v>0.53</v>
@@ -2955,8 +2996,8 @@
       <c r="A25" s="2">
         <v>23</v>
       </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="78" t="s">
+      <c r="B25" s="94"/>
+      <c r="C25" s="72" t="s">
         <v>44</v>
       </c>
       <c r="D25" s="9" t="s">
@@ -2992,55 +3033,55 @@
       <c r="A26" s="2">
         <v>24</v>
       </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="81" t="s">
+      <c r="B26" s="95"/>
+      <c r="C26" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="D26" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="71" t="s">
+      <c r="E26" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="71" t="s">
+      <c r="F26" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="G26" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="72" t="s">
+      <c r="G26" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="I26" s="73" t="s">
+      <c r="I26" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="J26" s="74">
+      <c r="J26" s="118">
         <v>8</v>
       </c>
-      <c r="K26" s="75">
+      <c r="K26" s="119">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="L26" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="M26" s="72" t="s">
+      <c r="L26" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="M26" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="N26" s="73" t="s">
+      <c r="N26" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="O26" s="72" t="s">
-        <v>146</v>
-      </c>
-      <c r="P26" s="72" t="s">
+      <c r="O26" s="117" t="s">
+        <v>144</v>
+      </c>
+      <c r="P26" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="Q26" s="73" t="s">
+      <c r="Q26" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="R26" s="76" t="s">
-        <v>147</v>
+      <c r="R26" s="120" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="16.5" thickBot="1">
@@ -3050,18 +3091,18 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="97" t="s">
-        <v>148</v>
-      </c>
-      <c r="K27" s="97"/>
+      <c r="J27" s="96" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="96"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
-      <c r="O27" s="93"/>
+      <c r="O27" s="86"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="93">
+      <c r="Q27" s="86">
         <f>SUM(Q3:Q25)</f>
-        <v>405.23100000000005</v>
+        <v>404.50600000000009</v>
       </c>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -3073,21 +3114,21 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="98" t="s">
-        <v>151</v>
-      </c>
-      <c r="K28" s="98"/>
+      <c r="J28" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="K28" s="97"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="17">
         <f>SUM(O3:O25)</f>
-        <v>72.115000000000009</v>
+        <v>85.231000000000009</v>
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="17">
         <f>Q27/20</f>
-        <v>20.261550000000003</v>
+        <v>20.225300000000004</v>
       </c>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -3370,24 +3411,24 @@
     <hyperlink ref="M3" r:id="rId1"/>
     <hyperlink ref="M4" r:id="rId2"/>
     <hyperlink ref="M5" r:id="rId3"/>
-    <hyperlink ref="M6" r:id="rId4"/>
-    <hyperlink ref="M7" r:id="rId5"/>
-    <hyperlink ref="M8" r:id="rId6"/>
-    <hyperlink ref="M9" r:id="rId7"/>
-    <hyperlink ref="M10" r:id="rId8"/>
-    <hyperlink ref="M13" r:id="rId9"/>
-    <hyperlink ref="M14" r:id="rId10"/>
-    <hyperlink ref="M15" r:id="rId11"/>
-    <hyperlink ref="M16" r:id="rId12"/>
-    <hyperlink ref="M17" r:id="rId13"/>
-    <hyperlink ref="M18" r:id="rId14"/>
-    <hyperlink ref="M19" r:id="rId15"/>
-    <hyperlink ref="M20" r:id="rId16"/>
-    <hyperlink ref="M21" r:id="rId17"/>
-    <hyperlink ref="M23" r:id="rId18"/>
-    <hyperlink ref="M24" r:id="rId19"/>
-    <hyperlink ref="M22" r:id="rId20"/>
-    <hyperlink ref="M12" r:id="rId21"/>
+    <hyperlink ref="M7" r:id="rId4"/>
+    <hyperlink ref="M8" r:id="rId5"/>
+    <hyperlink ref="M9" r:id="rId6"/>
+    <hyperlink ref="M10" r:id="rId7"/>
+    <hyperlink ref="M13" r:id="rId8"/>
+    <hyperlink ref="M14" r:id="rId9"/>
+    <hyperlink ref="M15" r:id="rId10"/>
+    <hyperlink ref="M18" r:id="rId11"/>
+    <hyperlink ref="M20" r:id="rId12"/>
+    <hyperlink ref="M21" r:id="rId13"/>
+    <hyperlink ref="M23" r:id="rId14"/>
+    <hyperlink ref="M24" r:id="rId15"/>
+    <hyperlink ref="M22" r:id="rId16"/>
+    <hyperlink ref="M12" r:id="rId17"/>
+    <hyperlink ref="M6" r:id="rId18"/>
+    <hyperlink ref="M16" r:id="rId19"/>
+    <hyperlink ref="M17" r:id="rId20"/>
+    <hyperlink ref="M19" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId22"/>
